--- a/data/portfolios/portfolio_it_infosec.xlsx
+++ b/data/portfolios/portfolio_it_infosec.xlsx
@@ -36,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,8 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000078D4"/>
-        <bgColor rgb="000078D4"/>
+        <fgColor rgb="00004578"/>
+        <bgColor rgb="00004578"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005C6873"/>
+        <bgColor rgb="005C6873"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,10 +82,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,5901 +462,5901 @@
   <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="37" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="29" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="61" customWidth="1" min="32" max="32"/>
-    <col width="104" customWidth="1" min="33" max="33"/>
-    <col width="84" customWidth="1" min="34" max="34"/>
-    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="32" customWidth="1" min="30" max="30"/>
+    <col width="21" customWidth="1" min="31" max="31"/>
+    <col width="40" customWidth="1" min="32" max="32"/>
+    <col width="40" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="29" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Project ID</t>
+          <t>Project ID * [MANDATORY]</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Project Name</t>
+          <t>Project Name * [MANDATORY]</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio</t>
+          <t>Portfolio * [MANDATORY]</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Business Unit</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Executive Sponsor</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sponsor Level</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Project Status</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Go-Live Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Months to Go-Live</t>
+          <t>Business Unit * [MANDATORY]</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Site [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sponsor [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Sponsor Level [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Project Status [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Go-Live Date [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Months to Go-Live [OPTIONAL]</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Business Value (1-5)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Regulatory / Security</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Digital Transformation</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Protected Program</t>
+          <t>Business Value (1-5) * [MANDATORY]</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory / Security [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Digital Transformation [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Protected Program [OPTIONAL]</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Primary Skill</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Skill Demand (FTE)</t>
+          <t>Primary Skill * [MANDATORY]</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Skill Demand (FTE) [OPTIONAL]</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Cost Estimate (USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Dependency Count</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Rating</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Effort (Person-Weeks)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Completeness</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Model Certainty</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence Score</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence Level</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ML Tier</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Final Tier</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Priority Score</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Recommended Action</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Rule Overrides</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Top Drivers</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Data Issues</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Sources Present</t>
+          <t>Cost Estimate (USD) * [MANDATORY]</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Dependency Count [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Risk Rating [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Effort (Person-Weeks) [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Completeness [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Quality [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>Model Certainty [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Confidence Score [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Confidence Level [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>ML Tier [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Final Tier [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>Priority Score [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>Recommended Action [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>Cluster [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>Rule Overrides [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>Top Drivers [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>Data Issues [OPTIONAL]</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>Sources Present [OPTIONAL]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>GIS-0001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Edge Network Segmentation Refresh</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Semiconductor Process Equipment</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Mateo Okafor</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Dmitri Nakamura</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2028-06-02</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M2" s="3" t="b">
+      <c r="M2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="N2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Cloud and Infrastructure</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="4" t="n">
         <v>2635974</v>
       </c>
-      <c r="S2" s="3" t="n">
+      <c r="S2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="X2" s="3" t="n">
+      <c r="X2" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="4" t="n">
         <v>69.8</v>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" s="4" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.14); Regulatory / Security (+0.45); Cost Magnitude (-0.13)</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AI2" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>GIS-0002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Resilient Datacenter Consolidation Rollout</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Owen Brandt</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Hannah Tanaka</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2027-03-28</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="M3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Network Engineering</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="4" t="n">
         <v>10.1</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="4" t="n">
         <v>1574629</v>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="S3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="X3" s="3" t="n">
+      <c r="X3" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" s="4" t="n">
         <v>55.1</v>
       </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Re-sequence</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>R2 Executive Sponsorship</t>
         </is>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.36); Timing Urgency (+0.44); Regulatory / Security (-0.12); Cost Magnitude (-0.08)</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="3" t="n">
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="4" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>GIS-0003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Resilient Model Registry Migration</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Owen Brandt</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Leila Iyer</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2027-06-15</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="b">
+      <c r="M4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Cloud and Infrastructure</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="4" t="n">
         <v>2374835</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" s="4" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD4" s="2" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE4" s="2" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.38); Regulatory / Security (-0.12); Cost Magnitude (-0.12)</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="3" t="n">
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>GIS-0004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Identity-Led API Gateway Program</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Finance and Controls</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Avery Romero</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Lucas Schmidt</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="b">
+      <c r="M5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O5" s="3" t="b">
+      <c r="O5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Network Engineering</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="4" t="n">
         <v>8.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="4" t="n">
         <v>252072</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD5" s="2" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
         <is>
           <t>Protect slot</t>
         </is>
       </c>
-      <c r="AE5" s="2" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF5" s="2" t="inlineStr">
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <t>R3 Protected Program</t>
         </is>
       </c>
-      <c r="AG5" s="2" t="inlineStr">
+      <c r="AG5" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.54); Regulatory / Security (-0.12); Cost Magnitude (-0.01)</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="3" t="n">
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>GIS-0005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Resilient API Gateway Phase 2</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Fab Operations</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Avery Romero</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Yara Haddad</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="b">
+      <c r="M6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="4" t="n">
         <v>1983445</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="X6" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD6" s="2" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE6" s="2" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.64); Regulatory / Security (-0.12); Cost Magnitude (-0.10)</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="3" t="n">
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>GIS-0006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Unified Cloud Landing Zone Hardening</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Penang</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Mateo Schmidt</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Dmitri Nakamura</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2027-10-11</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="b">
+      <c r="M7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Data Engineering</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="4" t="n">
         <v>9.9</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="4" t="n">
         <v>1800000</v>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="Y7" s="3" t="n">
+      <c r="Y7" s="4" t="n">
         <v>63.3</v>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="AD7" s="2" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t>Add capacity</t>
         </is>
       </c>
-      <c r="AE7" s="2" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr">
+      <c r="AF7" s="3" t="inlineStr">
         <is>
           <t>R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG7" s="2" t="inlineStr">
+      <c r="AG7" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.30); Regulatory / Security (-0.12); Cost Magnitude (-0.09)</t>
         </is>
       </c>
-      <c r="AH7" s="2" t="inlineStr">
+      <c r="AH7" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI7" s="3" t="n">
+      <c r="AI7" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>GIS-0007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Automated Endpoint Hardening Upgrade</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Finance and Controls</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Samuel Haddad</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Dmitri Nakamura</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2027-05-03</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="3" t="b">
+      <c r="M8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="b">
+      <c r="N8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Project Management</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="4" t="n">
         <v>11.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="4" t="n">
         <v>2762706</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y8" s="4" t="n">
         <v>85.5</v>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD8" s="2" t="inlineStr">
+      <c r="AD8" s="3" t="inlineStr">
         <is>
           <t>Protect slot</t>
         </is>
       </c>
-      <c r="AE8" s="2" t="inlineStr">
+      <c r="AE8" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF8" s="2" t="inlineStr">
+      <c r="AF8" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First; R3 Protected Program</t>
         </is>
       </c>
-      <c r="AG8" s="2" t="inlineStr">
+      <c r="AG8" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.40); Regulatory / Security (+0.45); Cost Magnitude (-0.14)</t>
         </is>
       </c>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="3" t="n">
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GIS-0008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Next-Gen Key Vault Migration Program</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Human Resources</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Grace Lindqvist</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Avery Bauer</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>2027-10-01</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="M9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="4" t="n">
         <v>4195957</v>
       </c>
-      <c r="S9" s="3" t="n">
+      <c r="S9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="X9" s="3" t="n">
+      <c r="X9" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="Y9" s="3" t="n">
+      <c r="Y9" s="4" t="n">
         <v>69.8</v>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" s="4" t="n">
         <v>53.3</v>
       </c>
-      <c r="AD9" s="2" t="inlineStr">
+      <c r="AD9" s="3" t="inlineStr">
         <is>
           <t>Re-sequence</t>
         </is>
       </c>
-      <c r="AE9" s="2" t="inlineStr">
+      <c r="AE9" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="inlineStr">
+      <c r="AF9" s="3" t="inlineStr">
         <is>
           <t>R2 Executive Sponsorship; R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG9" s="2" t="inlineStr">
+      <c r="AG9" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.36); Timing Urgency (+0.30); Regulatory / Security (-0.12); Cost Magnitude (-0.21)</t>
         </is>
       </c>
-      <c r="AH9" s="2" t="inlineStr">
+      <c r="AH9" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI9" s="3" t="n">
+      <c r="AI9" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>GIS-0009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Zero-Trust Microsegmentation for Fab Floor</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Global Supply Chain</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Elena Rostova</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Yara Haddad</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>2027-12-27</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="b">
+      <c r="M10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Cloud and Infrastructure</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="4" t="n">
         <v>3200000</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y10" s="3" t="n">
+      <c r="Y10" s="4" t="n">
         <v>82.8</v>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC10" s="3" t="n">
+      <c r="AC10" s="4" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="AD10" s="2" t="inlineStr">
+      <c r="AD10" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE10" s="2" t="inlineStr">
+      <c r="AE10" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr">
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.26); Regulatory / Security (-0.12); Cost Magnitude (-0.16)</t>
         </is>
       </c>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="3" t="n">
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>GIS-0010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Resilient Collaboration Platform Program</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Semiconductor Process Equipment</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Jordan Okafor</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Ingrid Iyer</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>2027-07-13</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="M11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="4" t="n">
         <v>1438421</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="X11" s="3" t="n">
+      <c r="X11" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="Y11" s="4" t="n">
         <v>72.7</v>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC11" s="3" t="n">
+      <c r="AC11" s="4" t="n">
         <v>82.3</v>
       </c>
-      <c r="AD11" s="2" t="inlineStr">
+      <c r="AD11" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE11" s="2" t="inlineStr">
+      <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr">
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.36); Regulatory / Security (-0.12); Cost Magnitude (-0.07)</t>
         </is>
       </c>
-      <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="3" t="n">
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>GIS-0011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Resilient Service Desk Automation Upgrade</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Information Security</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Isabel Brandt</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Dmitri Nakamura</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="M12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="4" t="n">
         <v>9.1</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="4" t="n">
         <v>1481114</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y12" s="3" t="n">
+      <c r="Y12" s="4" t="n">
         <v>72.3</v>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC12" s="3" t="n">
+      <c r="AC12" s="4" t="n">
         <v>95.3</v>
       </c>
-      <c r="AD12" s="2" t="inlineStr">
+      <c r="AD12" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE12" s="2" t="inlineStr">
+      <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr">
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.50); Regulatory / Security (-0.12); Cost Magnitude (-0.07)</t>
         </is>
       </c>
-      <c r="AH12" s="2" t="inlineStr">
+      <c r="AH12" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AI12" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>GIS-0012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Resilient Key Vault Migration Rollout</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Chloe Lindqvist</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Ethan Novak</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>2027-08-22</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="b">
+      <c r="M13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="4" t="n">
         <v>629521</v>
       </c>
-      <c r="S13" s="3" t="n">
+      <c r="S13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="X13" s="3" t="n">
+      <c r="X13" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y13" s="3" t="n">
+      <c r="Y13" s="4" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
+      <c r="AB13" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC13" s="3" t="n">
+      <c r="AC13" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD13" s="2" t="inlineStr">
+      <c r="AD13" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE13" s="2" t="inlineStr">
+      <c r="AE13" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr">
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.34); Regulatory / Security (-0.12); Cost Magnitude (-0.03)</t>
         </is>
       </c>
-      <c r="AH13" s="2" t="inlineStr">
+      <c r="AH13" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI13" s="3" t="n">
+      <c r="AI13" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>GIS-0013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Resilient Key Vault Migration Program</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Information Security</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Mateo Schmidt</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Yara Haddad</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>2028-02-27</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="M14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="4" t="n">
         <v>3.7</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="4" t="n">
         <v>676703</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="Y14" s="3" t="n">
+      <c r="Y14" s="4" t="n">
         <v>66.8</v>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
+      <c r="AB14" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AC14" s="3" t="n">
+      <c r="AC14" s="4" t="n">
         <v>76.7</v>
       </c>
-      <c r="AD14" s="2" t="inlineStr">
+      <c r="AD14" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE14" s="2" t="inlineStr">
+      <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF14" s="2" t="inlineStr"/>
-      <c r="AG14" s="2" t="inlineStr">
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.22); Regulatory / Security (-0.12); Cost Magnitude (-0.03)</t>
         </is>
       </c>
-      <c r="AH14" s="2" t="inlineStr">
+      <c r="AH14" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI14" s="3" t="n">
+      <c r="AI14" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>GIS-0014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Privileged Access Management (PAM) Expansion</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Global Supply Chain</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Penang</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Liam O'Connor</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Samuel Lindqvist</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M15" s="3" t="b">
+      <c r="M15" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3" t="b">
+      <c r="N15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="4" t="n">
         <v>450000</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="Y15" s="4" t="n">
         <v>75.8</v>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC15" s="3" t="n">
+      <c r="AC15" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD15" s="2" t="inlineStr">
+      <c r="AD15" s="3" t="inlineStr">
         <is>
           <t>Protect slot</t>
         </is>
       </c>
-      <c r="AE15" s="2" t="inlineStr">
+      <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF15" s="2" t="inlineStr">
+      <c r="AF15" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First; R3 Protected Program</t>
         </is>
       </c>
-      <c r="AG15" s="2" t="inlineStr">
+      <c r="AG15" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.54); Regulatory / Security (+0.45); Cost Magnitude (-0.02)</t>
         </is>
       </c>
-      <c r="AH15" s="2" t="inlineStr"/>
-      <c r="AI15" s="3" t="n">
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>GIS-0015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Security Operations SIEM/SOAR Automation</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Chloe Lindqvist</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Avery Bauer</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>2028-01-21</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="b">
+      <c r="M16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="O16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>Project Management</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="4" t="n">
         <v>3.1</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="4" t="n">
         <v>450000</v>
       </c>
-      <c r="S16" s="3" t="n">
+      <c r="S16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="U16" s="4" t="n">
         <v>170</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="4" t="n">
         <v>0.53</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="X16" s="3" t="n">
+      <c r="X16" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="Y16" s="3" t="n">
+      <c r="Y16" s="4" t="n">
         <v>67.3</v>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
+      <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
+      <c r="AB16" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC16" s="3" t="n">
+      <c r="AC16" s="4" t="n">
         <v>89.2</v>
       </c>
-      <c r="AD16" s="2" t="inlineStr">
+      <c r="AD16" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE16" s="2" t="inlineStr">
+      <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF16" s="2" t="inlineStr">
+      <c r="AF16" s="3" t="inlineStr">
         <is>
           <t>R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG16" s="2" t="inlineStr">
+      <c r="AG16" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.24); Regulatory / Security (-0.12); Cost Magnitude (-0.02)</t>
         </is>
       </c>
-      <c r="AH16" s="2" t="inlineStr">
+      <c r="AH16" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources); High upstream dependency entanglement</t>
         </is>
       </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AI16" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>GIS-0016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Enterprise Cloud Posture Management</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Semiconductor Process Equipment</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Owen Brandt</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Yara Haddad</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>2027-07-20</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="M17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="4" t="n">
         <v>5.4</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="4" t="n">
         <v>2400000</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="S17" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="X17" s="3" t="n">
+      <c r="X17" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="Y17" s="3" t="n">
+      <c r="Y17" s="4" t="n">
         <v>76.2</v>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z17" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Candidate to deprioritize</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
+      <c r="AB17" s="3" t="inlineStr">
         <is>
           <t>Candidate to deprioritize</t>
         </is>
       </c>
-      <c r="AC17" s="3" t="n">
+      <c r="AC17" s="4" t="n">
         <v>40.2</v>
       </c>
-      <c r="AD17" s="2" t="inlineStr">
+      <c r="AD17" s="3" t="inlineStr">
         <is>
           <t>Pause or divert skills</t>
         </is>
       </c>
-      <c r="AE17" s="2" t="inlineStr">
+      <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF17" s="2" t="inlineStr">
+      <c r="AF17" s="3" t="inlineStr">
         <is>
           <t>R2 Executive Sponsorship; R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG17" s="2" t="inlineStr">
+      <c r="AG17" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.36); Timing Urgency (+0.36); Regulatory / Security (-0.12); Cost Magnitude (-0.12)</t>
         </is>
       </c>
-      <c r="AH17" s="2" t="inlineStr">
+      <c r="AH17" s="3" t="inlineStr">
         <is>
           <t>High upstream dependency entanglement</t>
         </is>
       </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AI17" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>GIS-0017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Threat Intelligence Exchange Platform</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Finance and Controls</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Tariq Aziz</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Klaus Weber</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>2028-07-20</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="M18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>Data Engineering</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="4" t="n">
         <v>1250000</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T18" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="X18" s="3" t="n">
+      <c r="X18" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="Y18" s="3" t="n">
+      <c r="Y18" s="4" t="n">
         <v>78.7</v>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="Z18" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>Candidate to deprioritize</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
+      <c r="AB18" s="3" t="inlineStr">
         <is>
           <t>Candidate to deprioritize</t>
         </is>
       </c>
-      <c r="AC18" s="3" t="n">
+      <c r="AC18" s="4" t="n">
         <v>41.3</v>
       </c>
-      <c r="AD18" s="2" t="inlineStr">
+      <c r="AD18" s="3" t="inlineStr">
         <is>
           <t>Pause or divert skills</t>
         </is>
       </c>
-      <c r="AE18" s="2" t="inlineStr">
+      <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF18" s="2" t="inlineStr">
+      <c r="AF18" s="3" t="inlineStr">
         <is>
           <t>R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG18" s="2" t="inlineStr">
+      <c r="AG18" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.12); Regulatory / Security (-0.12); Cost Magnitude (-0.06)</t>
         </is>
       </c>
-      <c r="AH18" s="2" t="inlineStr"/>
-      <c r="AI18" s="3" t="n">
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>GIS-0018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Automated Vulnerability Patch Orchestration</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Finance and Controls</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Elena Rostova</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Priya Aziz</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>2028-03-27</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="b">
+      <c r="M19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="O19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="4" t="n">
         <v>2400000</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="X19" s="3" t="n">
+      <c r="X19" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="Y19" s="3" t="n">
+      <c r="Y19" s="4" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="Z19" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
+      <c r="AB19" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC19" s="3" t="n">
+      <c r="AC19" s="4" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="AD19" s="2" t="inlineStr">
+      <c r="AD19" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE19" s="2" t="inlineStr">
+      <c r="AE19" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF19" s="2" t="inlineStr"/>
-      <c r="AG19" s="2" t="inlineStr">
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.20); Regulatory / Security (-0.12); Cost Magnitude (-0.12)</t>
         </is>
       </c>
-      <c r="AH19" s="2" t="inlineStr">
+      <c r="AH19" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI19" s="3" t="n">
+      <c r="AI19" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>GIS-0019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Next-Gen Access Certification Rollout</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Information Security</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Owen Brandt</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Priya Reyes</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="b">
+      <c r="M20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="O20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>Data Engineering</t>
         </is>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="4" t="n">
         <v>5020303</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="U20" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="X20" s="3" t="n">
+      <c r="X20" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="Y20" s="3" t="n">
+      <c r="Y20" s="4" t="n">
         <v>80.8</v>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
+      <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
+      <c r="AB20" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC20" s="3" t="n">
+      <c r="AC20" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD20" s="2" t="inlineStr">
+      <c r="AD20" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE20" s="2" t="inlineStr">
+      <c r="AE20" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF20" s="2" t="inlineStr"/>
-      <c r="AG20" s="2" t="inlineStr">
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.60); Regulatory / Security (-0.12); Cost Magnitude (-0.25)</t>
         </is>
       </c>
-      <c r="AH20" s="2" t="inlineStr"/>
-      <c r="AI20" s="3" t="n">
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>GIS-0020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Next-Gen SIEM Modernization Upgrade</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Information Security</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Ingrid Brandt</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Dmitri Nakamura</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>2028-02-13</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M21" s="3" t="b">
+      <c r="M21" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="b">
+      <c r="N21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="4" t="n">
         <v>11.9</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="4" t="n">
         <v>2277974</v>
       </c>
-      <c r="S21" s="3" t="n">
+      <c r="S21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="X21" s="3" t="n">
+      <c r="X21" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="Y21" s="3" t="n">
+      <c r="Y21" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
+      <c r="AB21" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC21" s="3" t="n">
+      <c r="AC21" s="4" t="n">
         <v>92.2</v>
       </c>
-      <c r="AD21" s="2" t="inlineStr">
+      <c r="AD21" s="3" t="inlineStr">
         <is>
           <t>Protect slot</t>
         </is>
       </c>
-      <c r="AE21" s="2" t="inlineStr">
+      <c r="AE21" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF21" s="2" t="inlineStr">
+      <c r="AF21" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First; R3 Protected Program</t>
         </is>
       </c>
-      <c r="AG21" s="2" t="inlineStr">
+      <c r="AG21" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.22); Regulatory / Security (+0.45); Cost Magnitude (-0.11)</t>
         </is>
       </c>
-      <c r="AH21" s="2" t="inlineStr"/>
-      <c r="AI21" s="3" t="n">
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>GIS-0021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Hardware Security Module (HSM) Fleet Refresh</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Carlos Moreno</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Victor Cruz</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M22" s="3" t="b">
+      <c r="M22" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N22" s="3" t="b">
+      <c r="N22" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="O22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="4" t="n">
         <v>2400000</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="S22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="X22" s="3" t="n">
+      <c r="X22" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="Y22" s="3" t="n">
+      <c r="Y22" s="4" t="n">
         <v>66.5</v>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
+      <c r="AB22" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC22" s="3" t="n">
+      <c r="AC22" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD22" s="2" t="inlineStr">
+      <c r="AD22" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE22" s="2" t="inlineStr">
+      <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF22" s="2" t="inlineStr">
+      <c r="AF22" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First</t>
         </is>
       </c>
-      <c r="AG22" s="2" t="inlineStr">
+      <c r="AG22" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.56); Regulatory / Security (+0.45); Cost Magnitude (-0.12)</t>
         </is>
       </c>
-      <c r="AH22" s="2" t="inlineStr">
+      <c r="AH22" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI22" s="3" t="n">
+      <c r="AI22" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>GIS-0022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Enterprise Data Loss Prevention (DLP) Wave 3</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Global Supply Chain</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Marcus Chen</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Lucas Schmidt</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>2028-07-24</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="M23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>Integration (iPaaS)</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="4" t="n">
         <v>10.9</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="4" t="n">
         <v>3200000</v>
       </c>
-      <c r="S23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="S23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U23" s="3" t="n">
+      <c r="U23" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="X23" s="3" t="n">
+      <c r="X23" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="Y23" s="3" t="n">
+      <c r="Y23" s="4" t="n">
         <v>76.8</v>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
+      <c r="AB23" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC23" s="3" t="n">
+      <c r="AC23" s="4" t="n">
         <v>90.5</v>
       </c>
-      <c r="AD23" s="2" t="inlineStr">
+      <c r="AD23" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE23" s="2" t="inlineStr">
+      <c r="AE23" s="3" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="AF23" s="2" t="inlineStr"/>
-      <c r="AG23" s="2" t="inlineStr">
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.12); Regulatory / Security (-0.12); Cost Magnitude (-0.16)</t>
         </is>
       </c>
-      <c r="AH23" s="2" t="inlineStr"/>
-      <c r="AI23" s="3" t="n">
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>GIS-0023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Next-Gen Service Desk Automation Migration</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Grace Lindqvist</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Priya Aziz</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>2027-11-10</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="b">
+      <c r="M24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="O24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="4" t="n">
         <v>951531</v>
       </c>
-      <c r="S24" s="3" t="n">
+      <c r="S24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="T24" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U24" s="3" t="n">
+      <c r="U24" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="X24" s="3" t="n">
+      <c r="X24" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="Y24" s="3" t="n">
+      <c r="Y24" s="4" t="n">
         <v>74.2</v>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z24" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
+      <c r="AB24" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC24" s="3" t="n">
+      <c r="AC24" s="4" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="AD24" s="2" t="inlineStr">
+      <c r="AD24" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE24" s="2" t="inlineStr">
+      <c r="AE24" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF24" s="2" t="inlineStr"/>
-      <c r="AG24" s="2" t="inlineStr">
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.28); Regulatory / Security (-0.12); Cost Magnitude (-0.05)</t>
         </is>
       </c>
-      <c r="AH24" s="2" t="inlineStr"/>
-      <c r="AI24" s="3" t="n">
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>GIS-0024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Cloud-First Backup Resilience Rollout</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Tariq Aziz</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Jordan Ferreira</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>2027-02-12</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="b">
+      <c r="M25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="O25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="4" t="n">
         <v>1977643</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T25" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="U25" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="Y25" s="3" t="n">
+      <c r="Y25" s="4" t="n">
         <v>70.7</v>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z25" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
+      <c r="AB25" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC25" s="3" t="n">
+      <c r="AC25" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="AD25" s="2" t="inlineStr">
+      <c r="AD25" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE25" s="2" t="inlineStr">
+      <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF25" s="2" t="inlineStr">
+      <c r="AF25" s="3" t="inlineStr">
         <is>
           <t>R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG25" s="2" t="inlineStr">
+      <c r="AG25" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.46); Regulatory / Security (-0.12); Cost Magnitude (-0.10)</t>
         </is>
       </c>
-      <c r="AH25" s="2" t="inlineStr">
+      <c r="AH25" s="3" t="inlineStr">
         <is>
           <t>Sparse cross-system presence (&lt; 7 sources)</t>
         </is>
       </c>
-      <c r="AI25" s="3" t="n">
+      <c r="AI25" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>GIS-0025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Unified Model Registry Refresh</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Information Security</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Penang</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Mateo Schmidt</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Ethan Novak</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>2028-02-12</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="M26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="4" t="n">
         <v>1755495</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="S26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="Y26" s="3" t="n">
+      <c r="Y26" s="4" t="n">
         <v>85.8</v>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z26" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
+      <c r="AB26" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AC26" s="3" t="n">
+      <c r="AC26" s="4" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="AD26" s="2" t="inlineStr">
+      <c r="AD26" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE26" s="2" t="inlineStr">
+      <c r="AE26" s="3" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="inlineStr"/>
-      <c r="AG26" s="2" t="inlineStr">
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.22); Regulatory / Security (-0.12); Cost Magnitude (-0.09)</t>
         </is>
       </c>
-      <c r="AH26" s="2" t="inlineStr"/>
-      <c r="AI26" s="3" t="n">
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>GIS-0026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Cloud Security Boundary Enforcement</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Mateo Okafor</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Avery Bauer</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>2027-07-14</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="M27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>Data Engineering</t>
         </is>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="4" t="n">
         <v>6500000</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="S27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="X27" s="3" t="n">
+      <c r="X27" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="Y27" s="3" t="n">
+      <c r="Y27" s="4" t="n">
         <v>81.3</v>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
+      <c r="AB27" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AC27" s="3" t="n">
+      <c r="AC27" s="4" t="n">
         <v>63.9</v>
       </c>
-      <c r="AD27" s="2" t="inlineStr">
+      <c r="AD27" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE27" s="2" t="inlineStr">
+      <c r="AE27" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF27" s="2" t="inlineStr">
+      <c r="AF27" s="3" t="inlineStr">
         <is>
           <t>R2 Executive Sponsorship</t>
         </is>
       </c>
-      <c r="AG27" s="2" t="inlineStr">
+      <c r="AG27" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.36); Regulatory / Security (-0.12); Cost Magnitude (-0.33)</t>
         </is>
       </c>
-      <c r="AH27" s="2" t="inlineStr"/>
-      <c r="AI27" s="3" t="n">
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="4" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>GIS-0027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Edge Data Catalog Refresh</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Fab Operations</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Global Remote</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Yara Walsh</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Ingrid Iyer</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>2027-02-22</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3" t="b">
+      <c r="M28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="O28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="4" t="n">
         <v>823542</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="T28" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="U28" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="X28" s="3" t="n">
+      <c r="X28" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="Y28" s="3" t="n">
+      <c r="Y28" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z28" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
+      <c r="AB28" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AC28" s="3" t="n">
+      <c r="AC28" s="4" t="n">
         <v>57.5</v>
       </c>
-      <c r="AD28" s="2" t="inlineStr">
+      <c r="AD28" s="3" t="inlineStr">
         <is>
           <t>Re-sequence</t>
         </is>
       </c>
-      <c r="AE28" s="2" t="inlineStr">
+      <c r="AE28" s="3" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="AF28" s="2" t="inlineStr">
+      <c r="AF28" s="3" t="inlineStr">
         <is>
           <t>R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG28" s="2" t="inlineStr">
+      <c r="AG28" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.36); Timing Urgency (+0.46); Regulatory / Security (-0.12); Cost Magnitude (-0.04)</t>
         </is>
       </c>
-      <c r="AH28" s="2" t="inlineStr"/>
-      <c r="AI28" s="3" t="n">
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>GIS-0028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Identity Governance &amp; Lifecycle Automation</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Human Resources</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Liam O'Connor</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Leila Iyer</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>2027-07-03</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M29" s="3" t="b">
+      <c r="M29" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="N29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>Project Management</t>
         </is>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="4" t="n">
         <v>2.4</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="4" t="n">
         <v>450000</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T29" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="Y29" s="3" t="n">
+      <c r="Y29" s="4" t="n">
         <v>74.8</v>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
+      <c r="Z29" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
+      <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
+      <c r="AB29" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC29" s="3" t="n">
+      <c r="AC29" s="4" t="n">
         <v>86.2</v>
       </c>
-      <c r="AD29" s="2" t="inlineStr">
+      <c r="AD29" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE29" s="2" t="inlineStr">
+      <c r="AE29" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF29" s="2" t="inlineStr">
+      <c r="AF29" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First</t>
         </is>
       </c>
-      <c r="AG29" s="2" t="inlineStr">
+      <c r="AG29" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.36); Regulatory / Security (+0.45); Cost Magnitude (-0.02)</t>
         </is>
       </c>
-      <c r="AH29" s="2" t="inlineStr"/>
-      <c r="AI29" s="3" t="n">
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>GIS-0029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Zero-Trust Service Desk Automation Program</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Leila Patel</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Priya Aziz</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>2027-08-10</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M30" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3" t="b">
+      <c r="M30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="4" t="n">
         <v>510000</v>
       </c>
-      <c r="S30" s="3" t="n">
+      <c r="S30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T30" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U30" s="3" t="n">
+      <c r="U30" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="X30" s="3" t="n">
+      <c r="X30" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y30" s="3" t="n">
+      <c r="Y30" s="4" t="n">
         <v>77.5</v>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z30" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
+      <c r="AB30" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC30" s="3" t="n">
+      <c r="AC30" s="4" t="n">
         <v>91.7</v>
       </c>
-      <c r="AD30" s="2" t="inlineStr">
+      <c r="AD30" s="3" t="inlineStr">
         <is>
           <t>Protect slot</t>
         </is>
       </c>
-      <c r="AE30" s="2" t="inlineStr">
+      <c r="AE30" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF30" s="2" t="inlineStr">
+      <c r="AF30" s="3" t="inlineStr">
         <is>
           <t>R3 Protected Program</t>
         </is>
       </c>
-      <c r="AG30" s="2" t="inlineStr">
+      <c r="AG30" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.34); Regulatory / Security (-0.12); Cost Magnitude (-0.03)</t>
         </is>
       </c>
-      <c r="AH30" s="2" t="inlineStr"/>
-      <c r="AI30" s="3" t="n">
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>GIS-0030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Identity-Led Identity Federation Program</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Customer Services</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Carlos Moreno</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Yara Iyer</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>2027-07-02</t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M31" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="b">
+      <c r="M31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O31" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="O31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>Network Engineering</t>
         </is>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="4" t="n">
         <v>4780051</v>
       </c>
-      <c r="S31" s="3" t="n">
+      <c r="S31" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="X31" s="3" t="n">
+      <c r="X31" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="Y31" s="3" t="n">
+      <c r="Y31" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z31" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
+      <c r="AB31" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC31" s="3" t="n">
+      <c r="AC31" s="4" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="AD31" s="2" t="inlineStr">
+      <c r="AD31" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE31" s="2" t="inlineStr">
+      <c r="AE31" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="AF31" s="2" t="inlineStr"/>
-      <c r="AG31" s="2" t="inlineStr">
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.36); Regulatory / Security (-0.12); Cost Magnitude (-0.24)</t>
         </is>
       </c>
-      <c r="AH31" s="2" t="inlineStr"/>
-      <c r="AI31" s="3" t="n">
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="4" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>GIS-0031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Secure Data Catalog Program</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Isabel Okafor</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Samuel Lindqvist</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>2027-04-20</t>
         </is>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="M32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
         <is>
           <t>Cloud and Infrastructure</t>
         </is>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="4" t="n">
         <v>5498832</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T32" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U32" s="3" t="n">
+      <c r="U32" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="X32" s="3" t="n">
+      <c r="X32" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="Y32" s="3" t="n">
+      <c r="Y32" s="4" t="n">
         <v>91.5</v>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z32" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
+      <c r="AB32" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AC32" s="3" t="n">
+      <c r="AC32" s="4" t="n">
         <v>54.9</v>
       </c>
-      <c r="AD32" s="2" t="inlineStr">
+      <c r="AD32" s="3" t="inlineStr">
         <is>
           <t>Re-sequence</t>
         </is>
       </c>
-      <c r="AE32" s="2" t="inlineStr">
+      <c r="AE32" s="3" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="AF32" s="2" t="inlineStr"/>
-      <c r="AG32" s="2" t="inlineStr">
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.36); Timing Urgency (+0.42); Regulatory / Security (-0.12); Cost Magnitude (-0.27)</t>
         </is>
       </c>
-      <c r="AH32" s="2" t="inlineStr"/>
-      <c r="AI32" s="3" t="n">
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>GIS-0032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Cloud-First Data Catalog Upgrade</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Jordan Okafor</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Priya Aziz</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>2027-06-09</t>
         </is>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="M33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>Network Engineering</t>
         </is>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="4" t="n">
         <v>9.4</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="4" t="n">
         <v>2291540</v>
       </c>
-      <c r="S33" s="3" t="n">
+      <c r="S33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="4" t="n">
         <v>197</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="X33" s="3" t="n">
+      <c r="X33" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="Y33" s="3" t="n">
+      <c r="Y33" s="4" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="Z33" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
+      <c r="AB33" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC33" s="3" t="n">
+      <c r="AC33" s="4" t="n">
         <v>89.7</v>
       </c>
-      <c r="AD33" s="2" t="inlineStr">
+      <c r="AD33" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE33" s="2" t="inlineStr">
+      <c r="AE33" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF33" s="2" t="inlineStr"/>
-      <c r="AG33" s="2" t="inlineStr">
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.38); Regulatory / Security (-0.12); Cost Magnitude (-0.11)</t>
         </is>
       </c>
-      <c r="AH33" s="2" t="inlineStr"/>
-      <c r="AI33" s="3" t="n">
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="4" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>GIS-0033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Secure Patch Orchestration Refresh</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Finance and Controls</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Jordan Okafor</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Ingrid Iyer</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>2027-11-09</t>
         </is>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N34" s="3" t="b">
+      <c r="M34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O34" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="O34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="4" t="n">
         <v>1290000</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="S34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y34" s="3" t="n">
+      <c r="Y34" s="4" t="n">
         <v>78.3</v>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z34" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>Candidate to deprioritize</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
+      <c r="AB34" s="3" t="inlineStr">
         <is>
           <t>Candidate to deprioritize</t>
         </is>
       </c>
-      <c r="AC34" s="3" t="n">
+      <c r="AC34" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="AD34" s="2" t="inlineStr">
+      <c r="AD34" s="3" t="inlineStr">
         <is>
           <t>Pause or divert skills</t>
         </is>
       </c>
-      <c r="AE34" s="2" t="inlineStr">
+      <c r="AE34" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF34" s="2" t="inlineStr"/>
-      <c r="AG34" s="2" t="inlineStr">
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.18); Timing Urgency (+0.28); Regulatory / Security (-0.12); Cost Magnitude (-0.06)</t>
         </is>
       </c>
-      <c r="AH34" s="2" t="inlineStr"/>
-      <c r="AI34" s="3" t="n">
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>GIS-0034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Secure Service Desk Automation Rollout</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Digital Transformation</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Hsinchu</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Owen Aziz</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Yara Haddad</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>2027-03-15</t>
         </is>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="M35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>Cloud and Infrastructure</t>
         </is>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="4" t="n">
         <v>356206</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U35" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="X35" s="3" t="n">
+      <c r="X35" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y35" s="3" t="n">
+      <c r="Y35" s="4" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="Z35" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
+      <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
+      <c r="AB35" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AC35" s="3" t="n">
+      <c r="AC35" s="4" t="n">
         <v>57.5</v>
       </c>
-      <c r="AD35" s="2" t="inlineStr">
+      <c r="AD35" s="3" t="inlineStr">
         <is>
           <t>Re-sequence</t>
         </is>
       </c>
-      <c r="AE35" s="2" t="inlineStr">
+      <c r="AE35" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF35" s="2" t="inlineStr"/>
-      <c r="AG35" s="2" t="inlineStr">
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.44); Regulatory / Security (-0.12); Cost Magnitude (-0.02)</t>
         </is>
       </c>
-      <c r="AH35" s="2" t="inlineStr"/>
-      <c r="AI35" s="3" t="n">
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>GIS-0035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Enterprise Ticketing Integration Upgrade</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Corporate IT</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Avery Romero</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Ethan Novak</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>2028-06-22</t>
         </is>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M36" s="3" t="b">
+      <c r="M36" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N36" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O36" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="N36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="4" t="n">
         <v>4207688</v>
       </c>
-      <c r="S36" s="3" t="n">
+      <c r="S36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="T36" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="U36" s="4" t="n">
         <v>169</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="X36" s="3" t="n">
+      <c r="X36" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="Y36" s="3" t="n">
+      <c r="Y36" s="4" t="n">
         <v>72.8</v>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z36" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
+      <c r="AB36" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC36" s="3" t="n">
+      <c r="AC36" s="4" t="n">
         <v>49.4</v>
       </c>
-      <c r="AD36" s="2" t="inlineStr">
+      <c r="AD36" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE36" s="2" t="inlineStr">
+      <c r="AE36" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF36" s="2" t="inlineStr">
+      <c r="AF36" s="3" t="inlineStr">
         <is>
           <t>R1 Regulatory First; R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG36" s="2" t="inlineStr">
+      <c r="AG36" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.18); Timing Urgency (+0.14); Regulatory / Security (+0.45); Cost Magnitude (-0.21)</t>
         </is>
       </c>
-      <c r="AH36" s="2" t="inlineStr"/>
-      <c r="AI36" s="3" t="n">
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>GIS-0036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Cyber Defense SOC Playbook Orchestration</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Penang</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Owen Aziz</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Samuel Lindqvist</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>2027-10-10</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37" s="3" t="b">
+      <c r="M37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="O37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>Network Engineering</t>
         </is>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="4" t="n">
         <v>3132457</v>
       </c>
-      <c r="S37" s="3" t="n">
+      <c r="S37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T37" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U37" s="3" t="n">
+      <c r="U37" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="X37" s="3" t="n">
+      <c r="X37" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="Y37" s="3" t="n">
+      <c r="Y37" s="4" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="Z37" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
+      <c r="AB37" s="3" t="inlineStr">
         <is>
           <t>Can wait</t>
         </is>
       </c>
-      <c r="AC37" s="3" t="n">
+      <c r="AC37" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD37" s="2" t="inlineStr">
+      <c r="AD37" s="3" t="inlineStr">
         <is>
           <t>Re-sequence</t>
         </is>
       </c>
-      <c r="AE37" s="2" t="inlineStr">
+      <c r="AE37" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF37" s="2" t="inlineStr">
+      <c r="AF37" s="3" t="inlineStr">
         <is>
           <t>R2 Executive Sponsorship; R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG37" s="2" t="inlineStr">
+      <c r="AG37" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.36); Timing Urgency (+0.30); Regulatory / Security (-0.12); Cost Magnitude (-0.16)</t>
         </is>
       </c>
-      <c r="AH37" s="2" t="inlineStr"/>
-      <c r="AI37" s="3" t="n">
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>GIS-0037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Zero Trust Network Access (ZTNA) Deployment</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Fab Operations</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Priya Okafor</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Jordan Moreno</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>2027-01-21</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="M38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
         <is>
           <t>Unified Communications</t>
         </is>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="4" t="n">
         <v>11.1</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="4" t="n">
         <v>599099</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="S38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="X38" s="3" t="n">
+      <c r="X38" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="Y38" s="3" t="n">
+      <c r="Y38" s="4" t="n">
         <v>78.3</v>
       </c>
-      <c r="Z38" s="2" t="inlineStr">
+      <c r="Z38" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
+      <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
+      <c r="AB38" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC38" s="3" t="n">
+      <c r="AC38" s="4" t="n">
         <v>90.5</v>
       </c>
-      <c r="AD38" s="2" t="inlineStr">
+      <c r="AD38" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE38" s="2" t="inlineStr">
+      <c r="AE38" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF38" s="2" t="inlineStr"/>
-      <c r="AG38" s="2" t="inlineStr">
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.48); Regulatory / Security (-0.12); Cost Magnitude (-0.03)</t>
         </is>
       </c>
-      <c r="AH38" s="2" t="inlineStr"/>
-      <c r="AI38" s="3" t="n">
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>GIS-0038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Secure Cloud DevOps Pipeline Verification</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Semiconductor Process Equipment</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Tualatin</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Yara Gallagher</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Nadia Novak</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>2028-01-06</t>
         </is>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="M39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>Integration (iPaaS)</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="4" t="n">
         <v>1160629</v>
       </c>
-      <c r="S39" s="3" t="n">
+      <c r="S39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="T39" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="U39" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="Y39" s="3" t="n">
+      <c r="Y39" s="4" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z39" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
+      <c r="AB39" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC39" s="3" t="n">
+      <c r="AC39" s="4" t="n">
         <v>93.7</v>
       </c>
-      <c r="AD39" s="2" t="inlineStr">
+      <c r="AD39" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE39" s="2" t="inlineStr">
+      <c r="AE39" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="AF39" s="2" t="inlineStr"/>
-      <c r="AG39" s="2" t="inlineStr">
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.90); Timing Urgency (+0.24); Regulatory / Security (-0.12); Cost Magnitude (-0.06)</t>
         </is>
       </c>
-      <c r="AH39" s="2" t="inlineStr"/>
-      <c r="AI39" s="3" t="n">
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>GIS-0039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Third-Party Risk Assessment Engine</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Information Security</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Isabel Brandt</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Priya Aziz</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>2027-07-11</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40" s="3" t="b">
+      <c r="M40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="O40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
         <is>
           <t>Project Management</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="4" t="n">
         <v>2.3</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="4" t="n">
         <v>1800000</v>
       </c>
-      <c r="S40" s="3" t="n">
+      <c r="S40" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="T40" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="U40" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="Y40" s="3" t="n">
+      <c r="Y40" s="4" t="n">
         <v>86.3</v>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="Z40" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
+      <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
+      <c r="AB40" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC40" s="3" t="n">
+      <c r="AC40" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="AD40" s="2" t="inlineStr">
+      <c r="AD40" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE40" s="2" t="inlineStr">
+      <c r="AE40" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF40" s="2" t="inlineStr"/>
-      <c r="AG40" s="2" t="inlineStr">
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.72); Timing Urgency (+0.36); Regulatory / Security (-0.12); Cost Magnitude (-0.09)</t>
         </is>
       </c>
-      <c r="AH40" s="2" t="inlineStr"/>
-      <c r="AI40" s="3" t="n">
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="4" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>GIS-0040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Cryptographic Asset Discovery &amp; Audit</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>IT InfoSec</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Corporate IT</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Fremont</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Isabel Brandt</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Samuel Lindqvist</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="M41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>Network Engineering</t>
         </is>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="4" t="n">
         <v>443756</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T41" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="U41" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="X41" s="3" t="n">
+      <c r="X41" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y41" s="3" t="n">
+      <c r="Y41" s="4" t="n">
         <v>76.8</v>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z41" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
+      <c r="AB41" s="3" t="inlineStr">
         <is>
           <t>Must-do-now</t>
         </is>
       </c>
-      <c r="AC41" s="3" t="n">
+      <c r="AC41" s="4" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="AD41" s="2" t="inlineStr">
+      <c r="AD41" s="3" t="inlineStr">
         <is>
           <t>Proceed</t>
         </is>
       </c>
-      <c r="AE41" s="2" t="inlineStr">
+      <c r="AE41" s="3" t="inlineStr">
         <is>
           <t>Core IT</t>
         </is>
       </c>
-      <c r="AF41" s="2" t="inlineStr">
+      <c r="AF41" s="3" t="inlineStr">
         <is>
           <t>R5 Cross-Portfolio Critical Path</t>
         </is>
       </c>
-      <c r="AG41" s="2" t="inlineStr">
+      <c r="AG41" s="3" t="inlineStr">
         <is>
           <t>Business Value (+0.54); Timing Urgency (+0.64); Regulatory / Security (-0.12); Cost Magnitude (-0.02)</t>
         </is>
       </c>
-      <c r="AH41" s="2" t="inlineStr"/>
-      <c r="AI41" s="3" t="n">
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="4" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/portfolios/portfolio_it_infosec.xlsx
+++ b/data/portfolios/portfolio_it_infosec.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT InfoSec" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT - InfoSec" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IT InfoSec</t>
+          <t>IT - InfoSec</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
